--- a/data_pipeline/ultimate_selection.xlsx
+++ b/data_pipeline/ultimate_selection.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\internship\airflow\dbt_project\data_pipeline\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C8BE58C3-E1B5-42E0-AC58-A58FA3A65451}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{85F54633-01C5-44C8-977F-13465E1966EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -62,10 +62,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>Cape_Code</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>Chain_ladder</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -75,6 +71,10 @@
   </si>
   <si>
     <t>why?</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Cape_cod</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -449,6 +449,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:H11"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="7" max="7" width="13.3984375" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
@@ -496,10 +499,10 @@
         <v>2019</v>
       </c>
       <c r="G2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
@@ -522,10 +525,10 @@
         <v>2020</v>
       </c>
       <c r="G3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H3" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.3">
@@ -551,7 +554,7 @@
         <v>12</v>
       </c>
       <c r="H4" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.3">
@@ -577,7 +580,7 @@
         <v>12</v>
       </c>
       <c r="H5" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.3">
@@ -603,7 +606,7 @@
         <v>12</v>
       </c>
       <c r="H6" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.3">
@@ -626,10 +629,10 @@
         <v>2019</v>
       </c>
       <c r="G7" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H7" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.3">
@@ -652,10 +655,10 @@
         <v>2020</v>
       </c>
       <c r="G8" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H8" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.3">
@@ -678,10 +681,10 @@
         <v>2021</v>
       </c>
       <c r="G9" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H9" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.3">
@@ -707,7 +710,7 @@
         <v>12</v>
       </c>
       <c r="H10" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.3">
@@ -730,10 +733,10 @@
         <v>2023</v>
       </c>
       <c r="G11" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="H11" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
   </sheetData>

--- a/data_pipeline/ultimate_selection.xlsx
+++ b/data_pipeline/ultimate_selection.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\internship\airflow\dbt_project\data_pipeline\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{85F54633-01C5-44C8-977F-13465E1966EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB95342B-2C09-4C0A-9BE9-4A0174A42902}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="19">
   <si>
     <t>SEGMENTATION_VERSION</t>
   </si>
@@ -62,19 +62,27 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
+    <t>Cape_cod</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
     <t>Chain_ladder</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>why</t>
+    <t>Judgement</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>why?</t>
+    <t>Chain_ladder_paid</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>Cape_cod</t>
+    <t>Chain_ladder_incurred</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>a</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -447,11 +455,8 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H11"/>
+  <dimension ref="A1:H9"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="7" max="7" width="13.3984375" customWidth="1"/>
-  </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
@@ -496,13 +501,13 @@
         <v>10</v>
       </c>
       <c r="F2">
-        <v>2019</v>
+        <v>2020</v>
       </c>
       <c r="G2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="H2" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
@@ -522,13 +527,13 @@
         <v>10</v>
       </c>
       <c r="F3">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="G3" t="s">
         <v>13</v>
       </c>
       <c r="H3" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.3">
@@ -548,13 +553,13 @@
         <v>10</v>
       </c>
       <c r="F4">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="G4" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="H4" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.3">
@@ -574,13 +579,13 @@
         <v>10</v>
       </c>
       <c r="F5">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="G5" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="H5" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.3">
@@ -588,7 +593,7 @@
         <v>8</v>
       </c>
       <c r="B6" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C6" t="s">
         <v>10</v>
@@ -600,13 +605,13 @@
         <v>10</v>
       </c>
       <c r="F6">
-        <v>2023</v>
+        <v>2020</v>
       </c>
       <c r="G6" t="s">
         <v>12</v>
       </c>
       <c r="H6" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.3">
@@ -626,13 +631,13 @@
         <v>10</v>
       </c>
       <c r="F7">
-        <v>2019</v>
+        <v>2021</v>
       </c>
       <c r="G7" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="H7" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.3">
@@ -652,13 +657,13 @@
         <v>10</v>
       </c>
       <c r="F8">
-        <v>2020</v>
+        <v>2022</v>
       </c>
       <c r="G8" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="H8" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.3">
@@ -678,65 +683,13 @@
         <v>10</v>
       </c>
       <c r="F9">
-        <v>2021</v>
+        <v>2023</v>
       </c>
       <c r="G9" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="H9" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A10" t="s">
-        <v>8</v>
-      </c>
-      <c r="B10" t="s">
-        <v>11</v>
-      </c>
-      <c r="C10" t="s">
-        <v>10</v>
-      </c>
-      <c r="D10" t="s">
-        <v>10</v>
-      </c>
-      <c r="E10" t="s">
-        <v>10</v>
-      </c>
-      <c r="F10">
-        <v>2022</v>
-      </c>
-      <c r="G10" t="s">
-        <v>12</v>
-      </c>
-      <c r="H10" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A11" t="s">
-        <v>8</v>
-      </c>
-      <c r="B11" t="s">
-        <v>11</v>
-      </c>
-      <c r="C11" t="s">
-        <v>10</v>
-      </c>
-      <c r="D11" t="s">
-        <v>10</v>
-      </c>
-      <c r="E11" t="s">
-        <v>10</v>
-      </c>
-      <c r="F11">
-        <v>2023</v>
-      </c>
-      <c r="G11" t="s">
-        <v>16</v>
-      </c>
-      <c r="H11" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
   </sheetData>
